--- a/data/trans_camb/P1418-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P1418-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-2,31</t>
+          <t>-2,28</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-6,14</t>
+          <t>-6,22</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-4,19</t>
+          <t>-4,2</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 1,94</t>
+          <t>-4,24; 1,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 0,44</t>
+          <t>-5,04; 0,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 0,04</t>
+          <t>-5,42; -0,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 4,42</t>
+          <t>-5,58; 4,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 5,61</t>
+          <t>-3,36; 6,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,44; -2,93</t>
+          <t>-10,62; -2,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 2,52</t>
+          <t>-3,28; 2,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 2,35</t>
+          <t>-3,49; 2,56</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,7; -1,95</t>
+          <t>-6,76; -1,98</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-57,46%</t>
+          <t>-56,76%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-69,83%</t>
+          <t>-70,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-65,93%</t>
+          <t>-66,08%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-71,46; 78,63</t>
+          <t>-70,79; 70,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-84,49; 33,27</t>
+          <t>-84,28; 29,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-88,58; 11,19</t>
+          <t>-87,07; 7,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-50,38; 69,11</t>
+          <t>-48,63; 76,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-38,95; 89,26</t>
+          <t>-31,95; 103,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-84,25; -42,79</t>
+          <t>-85,04; -42,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-44,52; 58,17</t>
+          <t>-41,71; 57,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-41,64; 50,79</t>
+          <t>-42,84; 55,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-79,68; -38,78</t>
+          <t>-79,63; -39,13</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-3,65</t>
+          <t>-3,63</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-7,96</t>
+          <t>-8,07</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-5,86</t>
+          <t>-5,87</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,96; -0,47</t>
+          <t>-6,06; -0,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,1; -1,84</t>
+          <t>-6,85; -1,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,59; -1,31</t>
+          <t>-6,49; -1,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,79; -2,87</t>
+          <t>-10,43; -2,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,71; -5,5</t>
+          <t>-12,85; -5,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,31; -4,34</t>
+          <t>-11,83; -5,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,42; -2,77</t>
+          <t>-7,53; -2,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,95; -4,27</t>
+          <t>-8,95; -4,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,35; -3,83</t>
+          <t>-7,95; -3,44</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-61,48%</t>
+          <t>-61,08%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-57,72%</t>
+          <t>-58,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-59,11%</t>
+          <t>-59,21%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-80,21; -6,99</t>
+          <t>-78,94; -3,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-87,85; -33,63</t>
+          <t>-85,79; -39,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-82,1; -25,76</t>
+          <t>-81,32; -25,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-67,57; -24,27</t>
+          <t>-66,79; -22,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-79,76; -44,58</t>
+          <t>-78,44; -41,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-70,46; -39,74</t>
+          <t>-71,88; -41,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-65,61; -31,68</t>
+          <t>-65,84; -30,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-77,82; -49,27</t>
+          <t>-78,01; -50,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-72,29; -44,15</t>
+          <t>-70,64; -41,88</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,44</t>
+          <t>2,34</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,05</t>
+          <t>1,1</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 2,75</t>
+          <t>-2,53; 2,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 2,37</t>
+          <t>-2,95; 2,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 5,32</t>
+          <t>-0,68; 5,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 3,75</t>
+          <t>-4,48; 3,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 0,61</t>
+          <t>-6,55; 0,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 4,4</t>
+          <t>-3,02; 4,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 2,3</t>
+          <t>-2,85; 2,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 0,78</t>
+          <t>-3,56; 0,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 4,04</t>
+          <t>-0,76; 3,92</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,54%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-61,78; 124,08</t>
+          <t>-56,01; 141,34</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-59,55; 113,91</t>
+          <t>-60,2; 117,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-16,58; 230,55</t>
+          <t>-14,72; 266,78</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-47,37; 79,93</t>
+          <t>-51,0; 64,6</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-71,81; 17,43</t>
+          <t>-70,59; 20,85</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-30,08; 84,81</t>
+          <t>-31,08; 80,15</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-40,66; 53,36</t>
+          <t>-41,47; 51,76</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-59,07; 19,41</t>
+          <t>-55,72; 22,31</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-11,0; 97,64</t>
+          <t>-11,02; 96,21</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,81</t>
+          <t>0,76</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-3,33</t>
+          <t>-2,35</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-1,26</t>
+          <t>-0,79</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 3,66</t>
+          <t>-1,6; 3,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 0,81</t>
+          <t>-3,22; 1,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 3,76</t>
+          <t>-1,76; 3,52</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,12; 10,85</t>
+          <t>2,23; 11,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 0,99</t>
+          <t>-6,05; 0,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,2; -0,27</t>
+          <t>-5,87; 0,49</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,17; 6,66</t>
+          <t>0,92; 6,24</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 0,08</t>
+          <t>-4,2; 0,06</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 0,83</t>
+          <t>-3,04; 1,29</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-42,65%</t>
+          <t>-30,12%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-22,57%</t>
+          <t>-14,15%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-47,43; 156,78</t>
+          <t>-37,6; 179,94</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-77,65; 45,25</t>
+          <t>-76,12; 54,91</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-43,0; 177,55</t>
+          <t>-39,2; 166,37</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19,99; 179,6</t>
+          <t>22,2; 200,61</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-67,12; 15,09</t>
+          <t>-65,81; 15,28</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-68,4; -6,62</t>
+          <t>-57,08; 8,89</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,06; 155,13</t>
+          <t>13,33; 143,51</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-61,57; 2,24</t>
+          <t>-61,47; 6,04</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-51,25; 17,6</t>
+          <t>-44,88; 29,37</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-2,09</t>
+          <t>-2,39</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,05</t>
+          <t>-0,16</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,81</t>
+          <t>-1,11</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 4,14</t>
+          <t>-4,89; 3,61</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,64; -2,05</t>
+          <t>-8,86; -2,11</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 1,32</t>
+          <t>-6,47; 0,7</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 11,15</t>
+          <t>-1,79; 11,13</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-10,07; 1,12</t>
+          <t>-10,1; 1,06</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 4,67</t>
+          <t>-5,66; 4,49</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 5,98</t>
+          <t>-1,7; 5,79</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,75; -1,24</t>
+          <t>-8,28; -1,64</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 2,04</t>
+          <t>-4,53; 2,0</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-39,66%</t>
+          <t>-45,26%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-0,43%</t>
+          <t>-1,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-10,17%</t>
+          <t>-13,9%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-67,37; 144,91</t>
+          <t>-64,98; 115,72</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -0,58</t>
+          <t>-100,0; -38,79</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-77,26; 56,0</t>
+          <t>-76,36; 33,91</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-15,48; 146,42</t>
+          <t>-13,8; 148,61</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-72,08; 15,74</t>
+          <t>-71,22; 21,76</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-38,03; 62,17</t>
+          <t>-37,57; 64,19</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-17,55; 104,78</t>
+          <t>-18,43; 97,09</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-78,14; -18,75</t>
+          <t>-79,29; -22,48</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-41,0; 34,66</t>
+          <t>-43,62; 37,16</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4,72</t>
+          <t>4,6</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,56</t>
+          <t>4,58</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4,51</t>
+          <t>4,5</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 2,68</t>
+          <t>-3,14; 3,02</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 2,6</t>
+          <t>-3,16; 2,76</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,88; 7,83</t>
+          <t>1,45; 7,91</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 4,41</t>
+          <t>-6,04; 4,28</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-8,25; 1,44</t>
+          <t>-8,3; 0,89</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 9,58</t>
+          <t>0,07; 9,3</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 2,66</t>
+          <t>-3,34; 2,57</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 1,05</t>
+          <t>-4,88; 0,82</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1,58; 7,44</t>
+          <t>1,6; 7,09</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>131,01%</t>
+          <t>127,81%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>64,74%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-67,03; 133,25</t>
+          <t>-60,78; 174,74</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-67,17; 123,31</t>
+          <t>-61,48; 136,47</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8,75; 374,65</t>
+          <t>19,79; 386,91</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-45,1; 60,52</t>
+          <t>-47,17; 56,43</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-65,81; 20,34</t>
+          <t>-66,11; 14,65</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 123,25</t>
+          <t>-0,08; 126,1</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-40,59; 50,28</t>
+          <t>-39,89; 49,86</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-56,92; 24,09</t>
+          <t>-56,73; 15,53</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>14,74; 140,12</t>
+          <t>19,08; 136,85</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1,72</t>
+          <t>1,6</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,62</t>
+          <t>7,17</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3,1</t>
+          <t>4,52</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 1,51</t>
+          <t>-3,02; 1,79</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 0,63</t>
+          <t>-3,75; 0,69</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 4,57</t>
+          <t>-0,9; 4,21</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 5,79</t>
+          <t>-0,97; 5,69</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 4,6</t>
+          <t>-1,76; 4,87</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 8,88</t>
+          <t>4,02; 10,09</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 3,01</t>
+          <t>-1,24; 3,15</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 1,95</t>
+          <t>-2,04; 2,17</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 5,68</t>
+          <t>2,49; 6,83</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>65,16%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-51,31; 47,24</t>
+          <t>-49,98; 48,72</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-63,17; 19,54</t>
+          <t>-64,16; 21,44</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-19,72; 126,62</t>
+          <t>-16,21; 117,57</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 80,59</t>
+          <t>-9,38; 76,0</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-18,08; 62,0</t>
+          <t>-16,85; 64,47</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-35,32; 108,06</t>
+          <t>37,6; 135,67</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-14,79; 49,85</t>
+          <t>-15,27; 52,57</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-27,36; 32,54</t>
+          <t>-25,12; 37,64</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-15,51; 90,04</t>
+          <t>28,31; 115,06</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-6,53</t>
+          <t>-5,81</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-4,69</t>
+          <t>-5,39</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-5,93</t>
+          <t>-5,6</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-9,88; -5,5</t>
+          <t>-9,8; -5,46</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-9,19; -4,53</t>
+          <t>-8,81; -4,51</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-9,46; -4,34</t>
+          <t>-8,23; -3,4</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 0,02</t>
+          <t>-6,38; -0,27</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-6,98; -0,56</t>
+          <t>-7,05; -0,76</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-7,77; -1,98</t>
+          <t>-8,22; -2,93</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-7,41; -3,5</t>
+          <t>-7,24; -3,3</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-7,27; -3,24</t>
+          <t>-7,22; -3,29</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-8,33; -3,81</t>
+          <t>-7,55; -3,85</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-73,64%</t>
+          <t>-65,58%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-40,94%</t>
+          <t>-47,09%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-58,18%</t>
+          <t>-55,02%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-92,83; -73,16</t>
+          <t>-92,6; -70,25</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-86,58; -56,97</t>
+          <t>-86,05; -57,51</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-88,5; -56,32</t>
+          <t>-78,21; -46,23</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-50,28; -1,0</t>
+          <t>-48,05; -0,33</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-52,75; -5,67</t>
+          <t>-53,24; -6,91</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-57,95; -17,51</t>
+          <t>-62,08; -28,45</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-64,1; -37,2</t>
+          <t>-64,28; -37,35</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-64,16; -36,16</t>
+          <t>-62,69; -34,41</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-73,39; -40,96</t>
+          <t>-65,73; -41,87</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-1,44</t>
+          <t>-1,23</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-1,87</t>
+          <t>-1,33</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-1,63</t>
+          <t>-1,25</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-3,24; -1,4</t>
+          <t>-3,32; -1,35</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,94; -2,1</t>
+          <t>-4,01; -2,17</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-2,61; -0,4</t>
+          <t>-2,27; -0,26</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 1,29</t>
+          <t>-1,98; 1,02</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-4,33; -1,57</t>
+          <t>-4,53; -1,57</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-3,49; -0,41</t>
+          <t>-2,68; -0,02</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-2,21; -0,49</t>
+          <t>-2,23; -0,38</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-3,9; -2,21</t>
+          <t>-3,87; -2,15</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-2,65; -0,71</t>
+          <t>-2,08; -0,38</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-26,43%</t>
+          <t>-22,42%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-18,4%</t>
+          <t>-13,05%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-20,81%</t>
+          <t>-15,92%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-54,87; -27,79</t>
+          <t>-55,75; -27,55</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-65,98; -42,71</t>
+          <t>-66,86; -43,06</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-44,33; -8,25</t>
+          <t>-38,04; -5,53</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-16,13; 14,11</t>
+          <t>-17,69; 10,78</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-39,81; -15,61</t>
+          <t>-41,07; -17,04</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-32,99; -4,63</t>
+          <t>-24,06; -0,03</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-26,54; -6,29</t>
+          <t>-26,72; -4,96</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-45,74; -29,68</t>
+          <t>-46,79; -29,05</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-32,45; -10,04</t>
+          <t>-25,02; -5,12</t>
         </is>
       </c>
     </row>
